--- a/ig/ch-core/StructureDefinition-ch-core-contactpoint-ech-46-email.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-contactpoint-ech-46-email.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
